--- a/yolo像素預測_11_batch4.xlsx
+++ b/yolo像素預測_11_batch4.xlsx
@@ -544,38 +544,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>001_jpg.rf.26d64b4af7fce706bb3cba9a94640a2f.jpg</t>
+          <t>001_jpg.rf.1105af231b42e452e7cb1eda03ec9b04.jpg</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>0.729</v>
+        <v>0.762</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8172</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9317</v>
+        <v>0.9294</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9716</v>
+        <v>0.97</v>
       </c>
       <c r="G2" t="n">
-        <v>225.42</v>
+        <v>360.832</v>
       </c>
       <c r="H2" t="n">
-        <v>278.694</v>
+        <v>438.371</v>
       </c>
       <c r="I2" t="n">
-        <v>213.654</v>
+        <v>341.217</v>
       </c>
       <c r="J2" t="n">
-        <v>33.598</v>
+        <v>57.053</v>
       </c>
       <c r="K2" t="n">
-        <v>245.3777</v>
+        <v>381.822</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -583,35 +583,35 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>206.656</v>
+        <v>367.17</v>
       </c>
       <c r="N2" t="n">
-        <v>44.067</v>
+        <v>450.968</v>
       </c>
       <c r="O2" t="n">
-        <v>226.73</v>
+        <v>331.754</v>
       </c>
       <c r="P2" t="n">
-        <v>283.234</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>240.0085</v>
+        <v>384.1443</v>
       </c>
       <c r="R2" t="n">
-        <v>235.377</v>
+        <v>14.102</v>
       </c>
       <c r="S2" t="n">
-        <v>249.978</v>
+        <v>14.821</v>
       </c>
       <c r="T2" t="n">
-        <v>5.3691</v>
+        <v>-2.3223</v>
       </c>
       <c r="U2" t="n">
-        <v>2.237</v>
+        <v>0.605</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -628,38 +628,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>002_jpg.rf.ebe8c919bbe79621de3f9d2c2ed05e36.jpg</t>
+          <t>002_jpg.rf.c2f8eb01ea46264e4ea052a46e98be27.jpg</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.713</v>
+        <v>0.78</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8618</v>
+        <v>0.8599</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9284</v>
+        <v>0.925</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9472</v>
+        <v>0.9436</v>
       </c>
       <c r="G3" t="n">
-        <v>118.702</v>
+        <v>187.707</v>
       </c>
       <c r="H3" t="n">
-        <v>368.385</v>
+        <v>588.226</v>
       </c>
       <c r="I3" t="n">
-        <v>146.248</v>
+        <v>231.337</v>
       </c>
       <c r="J3" t="n">
-        <v>108.695</v>
+        <v>184.511</v>
       </c>
       <c r="K3" t="n">
-        <v>261.1464</v>
+        <v>406.0655</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -667,35 +667,35 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>155.773</v>
+        <v>171.905</v>
       </c>
       <c r="N3" t="n">
-        <v>151.742</v>
+        <v>609.873</v>
       </c>
       <c r="O3" t="n">
-        <v>112.704</v>
+        <v>247.235</v>
       </c>
       <c r="P3" t="n">
-        <v>382.001</v>
+        <v>245.907</v>
       </c>
       <c r="Q3" t="n">
-        <v>234.2528</v>
+        <v>371.6804</v>
       </c>
       <c r="R3" t="n">
-        <v>219.792</v>
+        <v>26.801</v>
       </c>
       <c r="S3" t="n">
-        <v>275.357</v>
+        <v>63.42</v>
       </c>
       <c r="T3" t="n">
-        <v>26.8936</v>
+        <v>34.3851</v>
       </c>
       <c r="U3" t="n">
-        <v>11.481</v>
+        <v>9.250999999999999</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -712,38 +712,38 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>003_jpg.rf.b1908a93192d25dce501afeee21c128c.jpg</t>
+          <t>003_jpg.rf.8c84e9e4fbafc67ed2555437d5b8a52e.jpg</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.774</v>
+        <v>0.843</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8348</v>
+        <v>0.8308</v>
       </c>
       <c r="E4" t="n">
-        <v>0.922</v>
+        <v>0.9272</v>
       </c>
       <c r="F4" t="n">
-        <v>0.968</v>
+        <v>0.967</v>
       </c>
       <c r="G4" t="n">
-        <v>187.525</v>
+        <v>300.168</v>
       </c>
       <c r="H4" t="n">
-        <v>374.015</v>
+        <v>588.045</v>
       </c>
       <c r="I4" t="n">
-        <v>198.383</v>
+        <v>311.016</v>
       </c>
       <c r="J4" t="n">
-        <v>75.095</v>
+        <v>135.629</v>
       </c>
       <c r="K4" t="n">
-        <v>299.117</v>
+        <v>452.5452</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -751,35 +751,35 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>201.506</v>
+        <v>283.82</v>
       </c>
       <c r="N4" t="n">
-        <v>72.782</v>
+        <v>606.061</v>
       </c>
       <c r="O4" t="n">
-        <v>176.55</v>
+        <v>320.872</v>
       </c>
       <c r="P4" t="n">
-        <v>378.078</v>
+        <v>122.327</v>
       </c>
       <c r="Q4" t="n">
-        <v>306.3144</v>
+        <v>485.1508</v>
       </c>
       <c r="R4" t="n">
-        <v>301.557</v>
+        <v>24.327</v>
       </c>
       <c r="S4" t="n">
-        <v>303.769</v>
+        <v>16.556</v>
       </c>
       <c r="T4" t="n">
-        <v>-7.1974</v>
+        <v>-32.6056</v>
       </c>
       <c r="U4" t="n">
-        <v>2.35</v>
+        <v>6.721</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -796,38 +796,38 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>004_jpg.rf.eff436d43ff0e4e14f3cf98402412e4c.jpg</t>
+          <t>004_jpg.rf.ffb9b06a9ac63eae161da9f9ef0a9120.jpg</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.753</v>
+        <v>0.792</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7755</v>
+        <v>0.7593</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8796</v>
+        <v>0.8711</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9143</v>
+        <v>0.9115</v>
       </c>
       <c r="G5" t="n">
-        <v>240.298</v>
+        <v>384.033</v>
       </c>
       <c r="H5" t="n">
-        <v>149.023</v>
+        <v>237.337</v>
       </c>
       <c r="I5" t="n">
-        <v>270.558</v>
+        <v>431.948</v>
       </c>
       <c r="J5" t="n">
-        <v>368.363</v>
+        <v>587.2619999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>221.4179</v>
+        <v>353.1902</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -835,35 +835,35 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>277.192</v>
+        <v>369.582</v>
       </c>
       <c r="N5" t="n">
-        <v>362.243</v>
+        <v>220.513</v>
       </c>
       <c r="O5" t="n">
-        <v>229.5</v>
+        <v>444.065</v>
       </c>
       <c r="P5" t="n">
-        <v>135.707</v>
+        <v>578.5549999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>231.5014</v>
+        <v>365.707</v>
       </c>
       <c r="R5" t="n">
-        <v>216.388</v>
+        <v>22.178</v>
       </c>
       <c r="S5" t="n">
-        <v>236.251</v>
+        <v>14.92</v>
       </c>
       <c r="T5" t="n">
-        <v>-10.0836</v>
+        <v>-12.5168</v>
       </c>
       <c r="U5" t="n">
-        <v>4.356</v>
+        <v>3.423</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -880,38 +880,38 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>005_jpg.rf.fd9c0ce3b040241497d9dc772869dbc0.jpg</t>
+          <t>005_jpg.rf.79ecb0061a063500188b8346999a17f1.jpg</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>0.852</v>
+        <v>0.861</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8209</v>
+        <v>0.8227</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9463</v>
+        <v>0.9458</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9665</v>
+        <v>0.965</v>
       </c>
       <c r="G6" t="n">
-        <v>193.809</v>
+        <v>309.514</v>
       </c>
       <c r="H6" t="n">
-        <v>338.909</v>
+        <v>542.0700000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>170.467</v>
+        <v>273.231</v>
       </c>
       <c r="J6" t="n">
-        <v>133.417</v>
+        <v>214.825</v>
       </c>
       <c r="K6" t="n">
-        <v>206.8139</v>
+        <v>329.2508</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -919,35 +919,35 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>155.333</v>
+        <v>316.64</v>
       </c>
       <c r="N6" t="n">
-        <v>107.222</v>
+        <v>578.5549999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>192.572</v>
+        <v>244.696</v>
       </c>
       <c r="P6" t="n">
-        <v>363.615</v>
+        <v>168.035</v>
       </c>
       <c r="Q6" t="n">
-        <v>259.0828</v>
+        <v>416.7771</v>
       </c>
       <c r="R6" t="n">
-        <v>234.86</v>
+        <v>37.174</v>
       </c>
       <c r="S6" t="n">
-        <v>231.257</v>
+        <v>54.805</v>
       </c>
       <c r="T6" t="n">
-        <v>-52.2689</v>
+        <v>-87.52630000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>20.175</v>
+        <v>21.001</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -964,38 +964,38 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>006_jpg.rf.23739e22d7c1ac7e038d6c1b63727b1b.jpg</t>
+          <t>006_jpg.rf.254e5f854c61e299003a39c7b21a13f9.jpg</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>0.705</v>
+        <v>0.733</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8404</v>
+        <v>0.835</v>
       </c>
       <c r="E7" t="n">
-        <v>0.925</v>
+        <v>0.9302</v>
       </c>
       <c r="F7" t="n">
-        <v>0.963</v>
+        <v>0.9649</v>
       </c>
       <c r="G7" t="n">
-        <v>204.669</v>
+        <v>328.513</v>
       </c>
       <c r="H7" t="n">
-        <v>344.342</v>
+        <v>548.402</v>
       </c>
       <c r="I7" t="n">
-        <v>213.961</v>
+        <v>339.161</v>
       </c>
       <c r="J7" t="n">
-        <v>65.497</v>
+        <v>108.973</v>
       </c>
       <c r="K7" t="n">
-        <v>278.999</v>
+        <v>439.5583</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1003,35 +1003,35 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>195.333</v>
+        <v>336.107</v>
       </c>
       <c r="N7" t="n">
-        <v>60.556</v>
+        <v>570.091</v>
       </c>
       <c r="O7" t="n">
-        <v>205.324</v>
+        <v>314.1</v>
       </c>
       <c r="P7" t="n">
-        <v>358.815</v>
+        <v>89.316</v>
       </c>
       <c r="Q7" t="n">
-        <v>298.4268</v>
+        <v>481.2781</v>
       </c>
       <c r="R7" t="n">
-        <v>283.94</v>
+        <v>22.98</v>
       </c>
       <c r="S7" t="n">
-        <v>293.445</v>
+        <v>31.85</v>
       </c>
       <c r="T7" t="n">
-        <v>-19.4278</v>
+        <v>-41.7198</v>
       </c>
       <c r="U7" t="n">
-        <v>6.51</v>
+        <v>8.669</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1048,38 +1048,38 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>007_jpg.rf.e90d85fcab8873bcc0c04824d0fd697a.jpg</t>
+          <t>007_jpg.rf.b8504246367036950d7bf74d5288bd85.jpg</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>0.721</v>
+        <v>0.765</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8447</v>
+        <v>0.8414</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9314</v>
+        <v>0.9352</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9528</v>
+        <v>0.9596</v>
       </c>
       <c r="G8" t="n">
-        <v>189.232</v>
+        <v>296.812</v>
       </c>
       <c r="H8" t="n">
-        <v>340.279</v>
+        <v>553.319</v>
       </c>
       <c r="I8" t="n">
-        <v>165.875</v>
+        <v>263.745</v>
       </c>
       <c r="J8" t="n">
-        <v>74.629</v>
+        <v>116.211</v>
       </c>
       <c r="K8" t="n">
-        <v>266.6748</v>
+        <v>438.3568</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1087,35 +1087,35 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>143.667</v>
+        <v>294.252</v>
       </c>
       <c r="N8" t="n">
-        <v>66.111</v>
+        <v>572.63</v>
       </c>
       <c r="O8" t="n">
-        <v>181.037</v>
+        <v>229.08</v>
       </c>
       <c r="P8" t="n">
-        <v>361.752</v>
+        <v>94.395</v>
       </c>
       <c r="Q8" t="n">
-        <v>297.9936</v>
+        <v>482.6558</v>
       </c>
       <c r="R8" t="n">
-        <v>277.928</v>
+        <v>19.48</v>
       </c>
       <c r="S8" t="n">
-        <v>287.524</v>
+        <v>40.959</v>
       </c>
       <c r="T8" t="n">
-        <v>-31.3187</v>
+        <v>-44.299</v>
       </c>
       <c r="U8" t="n">
-        <v>10.51</v>
+        <v>9.178000000000001</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1132,38 +1132,38 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>008_jpg.rf.a26cfdf2a008c9a3efb1c3741b326600.jpg</t>
+          <t>008_jpg.rf.a68611e3070f2b474779cc8dfa2e4a8c.jpg</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>0.736</v>
+        <v>0.799</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8428</v>
+        <v>0.8386</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9323</v>
+        <v>0.931</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9539</v>
+        <v>0.9563</v>
       </c>
       <c r="G9" t="n">
-        <v>187.608</v>
+        <v>300.15</v>
       </c>
       <c r="H9" t="n">
-        <v>332.636</v>
+        <v>531.179</v>
       </c>
       <c r="I9" t="n">
-        <v>194.918</v>
+        <v>306.867</v>
       </c>
       <c r="J9" t="n">
-        <v>84.795</v>
+        <v>140.462</v>
       </c>
       <c r="K9" t="n">
-        <v>247.9484</v>
+        <v>390.7747</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1171,35 +1171,35 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>175.956</v>
+        <v>317.226</v>
       </c>
       <c r="N9" t="n">
-        <v>108.017</v>
+        <v>538.2190000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>199.843</v>
+        <v>281.227</v>
       </c>
       <c r="P9" t="n">
-        <v>336.256</v>
+        <v>174.617</v>
       </c>
       <c r="Q9" t="n">
-        <v>229.4858</v>
+        <v>365.3802</v>
       </c>
       <c r="R9" t="n">
-        <v>224.921</v>
+        <v>18.47</v>
       </c>
       <c r="S9" t="n">
-        <v>251.509</v>
+        <v>42.708</v>
       </c>
       <c r="T9" t="n">
-        <v>18.4626</v>
+        <v>25.3945</v>
       </c>
       <c r="U9" t="n">
-        <v>8.045</v>
+        <v>6.95</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1216,38 +1216,38 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>009_jpg.rf.4df579de97813a043f771194b49e1a04.jpg</t>
+          <t>009_jpg.rf.657f1c50c198307029c735dd5f82ef61.jpg</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>0.681</v>
+        <v>0.767</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8514</v>
+        <v>0.8464</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9165</v>
+        <v>0.919</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9588</v>
+        <v>0.9584</v>
       </c>
       <c r="G10" t="n">
-        <v>208.938</v>
+        <v>334.134</v>
       </c>
       <c r="H10" t="n">
-        <v>390.715</v>
+        <v>615.41</v>
       </c>
       <c r="I10" t="n">
-        <v>247.372</v>
+        <v>390.042</v>
       </c>
       <c r="J10" t="n">
-        <v>88.173</v>
+        <v>153.476</v>
       </c>
       <c r="K10" t="n">
-        <v>304.9741</v>
+        <v>465.3046</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1255,35 +1255,35 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>230.181</v>
+        <v>318.709</v>
       </c>
       <c r="N10" t="n">
-        <v>131.869</v>
+        <v>614.735</v>
       </c>
       <c r="O10" t="n">
-        <v>202.479</v>
+        <v>362.157</v>
       </c>
       <c r="P10" t="n">
-        <v>386.873</v>
+        <v>208.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>256.5043</v>
+        <v>408.1843</v>
       </c>
       <c r="R10" t="n">
-        <v>259.717</v>
+        <v>15.44</v>
       </c>
       <c r="S10" t="n">
-        <v>302.055</v>
+        <v>62.017</v>
       </c>
       <c r="T10" t="n">
-        <v>48.4699</v>
+        <v>57.1203</v>
       </c>
       <c r="U10" t="n">
-        <v>18.896</v>
+        <v>13.994</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1300,38 +1300,38 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>010_jpg.rf.ec9d384ce8506ef686d26435bd5262e7.jpg</t>
+          <t>010_jpg.rf.eac5a5825bf03149622e75330479c716.jpg</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.708</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8022</v>
+        <v>0.8008</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9006</v>
+        <v>0.9086</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8971</v>
+        <v>0.9043</v>
       </c>
       <c r="G11" t="n">
-        <v>124.88</v>
+        <v>205.553</v>
       </c>
       <c r="H11" t="n">
-        <v>95.163</v>
+        <v>153.897</v>
       </c>
       <c r="I11" t="n">
-        <v>153.82</v>
+        <v>240.71</v>
       </c>
       <c r="J11" t="n">
-        <v>285.209</v>
+        <v>451.344</v>
       </c>
       <c r="K11" t="n">
-        <v>192.2366</v>
+        <v>299.5175</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1339,35 +1339,35 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>150.113</v>
+        <v>191.994</v>
       </c>
       <c r="N11" t="n">
-        <v>268.345</v>
+        <v>142.822</v>
       </c>
       <c r="O11" t="n">
-        <v>120.195</v>
+        <v>241.235</v>
       </c>
       <c r="P11" t="n">
-        <v>87.68600000000001</v>
+        <v>429.643</v>
       </c>
       <c r="Q11" t="n">
-        <v>183.1195</v>
+        <v>291.0171</v>
       </c>
       <c r="R11" t="n">
-        <v>175.01</v>
+        <v>17.507</v>
       </c>
       <c r="S11" t="n">
-        <v>200.365</v>
+        <v>21.707</v>
       </c>
       <c r="T11" t="n">
-        <v>9.117100000000001</v>
+        <v>8.500400000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>4.979</v>
+        <v>2.921</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1384,38 +1384,38 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>011_jpg.rf.188e8c8bdf31b26620d6221f09fd444a.jpg</t>
+          <t>011_jpg.rf.679bbc26bb36cbde35908160560ca1e1.jpg</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>0.828</v>
+        <v>0.897</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8152</v>
+        <v>0.8264</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8871</v>
+        <v>0.9447</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9732</v>
+        <v>0.9767</v>
       </c>
       <c r="G12" t="n">
-        <v>184.499</v>
+        <v>309.126</v>
       </c>
       <c r="H12" t="n">
-        <v>356.856</v>
+        <v>589.481</v>
       </c>
       <c r="I12" t="n">
-        <v>170.281</v>
+        <v>280.729</v>
       </c>
       <c r="J12" t="n">
-        <v>84.898</v>
+        <v>148.836</v>
       </c>
       <c r="K12" t="n">
-        <v>272.3296</v>
+        <v>441.5593</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1423,35 +1423,35 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>163.306</v>
+        <v>330.647</v>
       </c>
       <c r="N12" t="n">
-        <v>78.56999999999999</v>
+        <v>604.795</v>
       </c>
       <c r="O12" t="n">
-        <v>203.666</v>
+        <v>268.86</v>
       </c>
       <c r="P12" t="n">
-        <v>378.354</v>
+        <v>126.559</v>
       </c>
       <c r="Q12" t="n">
-        <v>302.4878</v>
+        <v>482.2103</v>
       </c>
       <c r="R12" t="n">
-        <v>279.092</v>
+        <v>26.414</v>
       </c>
       <c r="S12" t="n">
-        <v>295.349</v>
+        <v>25.241</v>
       </c>
       <c r="T12" t="n">
-        <v>-30.1582</v>
+        <v>-40.6511</v>
       </c>
       <c r="U12" t="n">
-        <v>9.970000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -1468,38 +1468,38 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>012_jpg.rf.95a4280570f81e990b0672e137123f00.jpg</t>
+          <t>012_jpg.rf.b15c84047d85689affd5e02d42e5bb7b.jpg</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>0.78</v>
+        <v>0.907</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7819</v>
+        <v>0.7925</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9098000000000001</v>
+        <v>0.9325</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9282</v>
+        <v>0.9529</v>
       </c>
       <c r="G13" t="n">
-        <v>284.205</v>
+        <v>449.921</v>
       </c>
       <c r="H13" t="n">
-        <v>331.209</v>
+        <v>521.253</v>
       </c>
       <c r="I13" t="n">
-        <v>245.277</v>
+        <v>390.96</v>
       </c>
       <c r="J13" t="n">
-        <v>92.816</v>
+        <v>165.001</v>
       </c>
       <c r="K13" t="n">
-        <v>241.5511</v>
+        <v>361.0982</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1507,35 +1507,35 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>240.889</v>
+        <v>472.842</v>
       </c>
       <c r="N13" t="n">
-        <v>91.667</v>
+        <v>554.855</v>
       </c>
       <c r="O13" t="n">
-        <v>298.052</v>
+        <v>374.66</v>
       </c>
       <c r="P13" t="n">
-        <v>346.906</v>
+        <v>131.638</v>
       </c>
       <c r="Q13" t="n">
-        <v>261.5622</v>
+        <v>434.4566</v>
       </c>
       <c r="R13" t="n">
-        <v>243.428</v>
+        <v>40.675</v>
       </c>
       <c r="S13" t="n">
-        <v>259.513</v>
+        <v>37.132</v>
       </c>
       <c r="T13" t="n">
-        <v>-20.0111</v>
+        <v>-73.3584</v>
       </c>
       <c r="U13" t="n">
-        <v>7.651</v>
+        <v>16.885</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -1552,38 +1552,38 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>013_jpg.rf.4c019428deb9ebda1a1031e06cf21b2d.jpg</t>
+          <t>013_jpg.rf.bce930629e64fe46f5220696f7ebfe27.jpg</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>0.762</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>0.837</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9510999999999999</v>
+        <v>0.9442</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9634</v>
+        <v>0.9567</v>
       </c>
       <c r="G14" t="n">
-        <v>188.154</v>
+        <v>297.954</v>
       </c>
       <c r="H14" t="n">
-        <v>347.228</v>
+        <v>551.437</v>
       </c>
       <c r="I14" t="n">
-        <v>173.431</v>
+        <v>270.736</v>
       </c>
       <c r="J14" t="n">
-        <v>73.64</v>
+        <v>149.01</v>
       </c>
       <c r="K14" t="n">
-        <v>273.9836</v>
+        <v>403.3465</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1591,35 +1591,35 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>158.016</v>
+        <v>290.02</v>
       </c>
       <c r="N14" t="n">
-        <v>91.79600000000001</v>
+        <v>583.634</v>
       </c>
       <c r="O14" t="n">
-        <v>180.213</v>
+        <v>250.239</v>
       </c>
       <c r="P14" t="n">
-        <v>364.686</v>
+        <v>157.031</v>
       </c>
       <c r="Q14" t="n">
-        <v>273.7913</v>
+        <v>428.4538</v>
       </c>
       <c r="R14" t="n">
-        <v>257.204</v>
+        <v>33.16</v>
       </c>
       <c r="S14" t="n">
-        <v>291.125</v>
+        <v>22.01</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1922</v>
+        <v>-25.1073</v>
       </c>
       <c r="U14" t="n">
-        <v>0.07000000000000001</v>
+        <v>5.86</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -1636,38 +1636,38 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>014_jpg.rf.3c16ab39680acc322316a655dbc99196.jpg</t>
+          <t>014_jpg.rf.24e022f786a07a1c33f55b9c8c117055.jpg</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>0.732</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7946</v>
+        <v>0.7847</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.9124</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9094</v>
+        <v>0.9285</v>
       </c>
       <c r="G15" t="n">
-        <v>162.575</v>
+        <v>270.894</v>
       </c>
       <c r="H15" t="n">
-        <v>27.968</v>
+        <v>36.753</v>
       </c>
       <c r="I15" t="n">
-        <v>206.319</v>
+        <v>329.053</v>
       </c>
       <c r="J15" t="n">
-        <v>253.219</v>
+        <v>399.979</v>
       </c>
       <c r="K15" t="n">
-        <v>229.4593</v>
+        <v>367.853</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1675,35 +1675,35 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>212.859</v>
+        <v>285.788</v>
       </c>
       <c r="N15" t="n">
-        <v>242.827</v>
+        <v>24.141</v>
       </c>
       <c r="O15" t="n">
-        <v>177.98</v>
+        <v>341.651</v>
       </c>
       <c r="P15" t="n">
-        <v>15.891</v>
+        <v>390.647</v>
       </c>
       <c r="Q15" t="n">
-        <v>229.6008</v>
+        <v>370.7389</v>
       </c>
       <c r="R15" t="n">
-        <v>220.665</v>
+        <v>19.517</v>
       </c>
       <c r="S15" t="n">
-        <v>239.014</v>
+        <v>15.678</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1415</v>
+        <v>-2.8858</v>
       </c>
       <c r="U15" t="n">
-        <v>0.062</v>
+        <v>0.778</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -1720,38 +1720,38 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>015_jpg.rf.73e9cf853e7b9c5474c463eab089c876.jpg</t>
+          <t>015_jpg.rf.5dc9f8101386549bc979b4c1502e2a8f.jpg</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7841</v>
+        <v>0.7808</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.9298</v>
       </c>
       <c r="F16" t="n">
-        <v>0.913</v>
+        <v>0.917</v>
       </c>
       <c r="G16" t="n">
-        <v>188.499</v>
+        <v>300.005</v>
       </c>
       <c r="H16" t="n">
-        <v>56.636</v>
+        <v>90.79600000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>219.784</v>
+        <v>352.78</v>
       </c>
       <c r="J16" t="n">
-        <v>286.115</v>
+        <v>457.395</v>
       </c>
       <c r="K16" t="n">
-        <v>231.6012</v>
+        <v>370.3783</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1759,35 +1759,35 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>216.154</v>
+        <v>306.102</v>
       </c>
       <c r="N16" t="n">
-        <v>288.334</v>
+        <v>72.387</v>
       </c>
       <c r="O16" t="n">
-        <v>191.118</v>
+        <v>345.883</v>
       </c>
       <c r="P16" t="n">
-        <v>43.902</v>
+        <v>460.901</v>
       </c>
       <c r="Q16" t="n">
-        <v>245.7106</v>
+        <v>390.5447</v>
       </c>
       <c r="R16" t="n">
-        <v>233.342</v>
+        <v>19.392</v>
       </c>
       <c r="S16" t="n">
-        <v>243.903</v>
+        <v>7.737</v>
       </c>
       <c r="T16" t="n">
-        <v>-14.1094</v>
+        <v>-20.1664</v>
       </c>
       <c r="U16" t="n">
-        <v>5.742</v>
+        <v>5.164</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -1804,38 +1804,38 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>016_jpg.rf.e4c9d7dfdf9ddac85121698887e3fcf9.jpg</t>
+          <t>016_jpg.rf.f43448224b15b8a6cd9f2d5ad9067753.jpg</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>0.827</v>
+        <v>0.854</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.7833</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9347</v>
+        <v>0.9384</v>
       </c>
       <c r="F17" t="n">
-        <v>0.917</v>
+        <v>0.9155</v>
       </c>
       <c r="G17" t="n">
-        <v>196.534</v>
+        <v>315.938</v>
       </c>
       <c r="H17" t="n">
-        <v>92.428</v>
+        <v>151.366</v>
       </c>
       <c r="I17" t="n">
-        <v>236.171</v>
+        <v>377.906</v>
       </c>
       <c r="J17" t="n">
-        <v>311.964</v>
+        <v>497.27</v>
       </c>
       <c r="K17" t="n">
-        <v>223.0859</v>
+        <v>351.4108</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1843,35 +1843,35 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>234.339</v>
+        <v>333.52</v>
       </c>
       <c r="N17" t="n">
-        <v>302.665</v>
+        <v>134.807</v>
       </c>
       <c r="O17" t="n">
-        <v>207.407</v>
+        <v>375.982</v>
       </c>
       <c r="P17" t="n">
-        <v>79.324</v>
+        <v>484.384</v>
       </c>
       <c r="Q17" t="n">
-        <v>224.9588</v>
+        <v>352.1467</v>
       </c>
       <c r="R17" t="n">
-        <v>213.609</v>
+        <v>24.153</v>
       </c>
       <c r="S17" t="n">
-        <v>234.412</v>
+        <v>13.029</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.8729</v>
+        <v>-0.7359</v>
       </c>
       <c r="U17" t="n">
-        <v>0.833</v>
+        <v>0.209</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -1888,38 +1888,38 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>017_jpg.rf.bcc03bba4330d37600812dfd900a6c98.jpg</t>
+          <t>017_jpg.rf.fcaf0815466137a033e3bc08d51d6407.jpg</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.828</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8537</v>
+        <v>0.8524</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8821</v>
+        <v>0.9405</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.9807</v>
       </c>
       <c r="G18" t="n">
-        <v>131.553</v>
+        <v>231.204</v>
       </c>
       <c r="H18" t="n">
-        <v>371.741</v>
+        <v>612.154</v>
       </c>
       <c r="I18" t="n">
-        <v>144.351</v>
+        <v>247.745</v>
       </c>
       <c r="J18" t="n">
-        <v>80.598</v>
+        <v>93.417</v>
       </c>
       <c r="K18" t="n">
-        <v>291.4238</v>
+        <v>519.0001</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1927,35 +1927,35 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>139.222</v>
+        <v>220.949</v>
       </c>
       <c r="N18" t="n">
-        <v>82.77800000000001</v>
+        <v>593.998</v>
       </c>
       <c r="O18" t="n">
-        <v>138.458</v>
+        <v>220.949</v>
       </c>
       <c r="P18" t="n">
-        <v>372.083</v>
+        <v>130.857</v>
       </c>
       <c r="Q18" t="n">
-        <v>289.3063</v>
+        <v>463.1407</v>
       </c>
       <c r="R18" t="n">
-        <v>289.065</v>
+        <v>20.852</v>
       </c>
       <c r="S18" t="n">
-        <v>291.545</v>
+        <v>46.04</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1174</v>
+        <v>55.8594</v>
       </c>
       <c r="U18" t="n">
-        <v>0.732</v>
+        <v>12.061</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -1972,38 +1972,38 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>018_jpg.rf.3f56a35aa4805306df0598026f7f051c.jpg</t>
+          <t>018_jpg.rf.185b2544ce10480d5e913c252ff83704.jpg</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>0.769</v>
+        <v>0.827</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8096</v>
+        <v>0.8116</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9417</v>
+        <v>0.9342</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9635</v>
+        <v>0.9613</v>
       </c>
       <c r="G19" t="n">
-        <v>219.957</v>
+        <v>349.487</v>
       </c>
       <c r="H19" t="n">
-        <v>344.426</v>
+        <v>552.306</v>
       </c>
       <c r="I19" t="n">
-        <v>190.997</v>
+        <v>303.923</v>
       </c>
       <c r="J19" t="n">
-        <v>135.138</v>
+        <v>215.159</v>
       </c>
       <c r="K19" t="n">
-        <v>211.2818</v>
+        <v>340.2121</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -2011,35 +2011,35 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>188.717</v>
+        <v>350.619</v>
       </c>
       <c r="N19" t="n">
-        <v>119.379</v>
+        <v>602.933</v>
       </c>
       <c r="O19" t="n">
-        <v>220.816</v>
+        <v>303.22</v>
       </c>
       <c r="P19" t="n">
-        <v>377.678</v>
+        <v>191.566</v>
       </c>
       <c r="Q19" t="n">
-        <v>260.2854</v>
+        <v>414.0888</v>
       </c>
       <c r="R19" t="n">
-        <v>227.205</v>
+        <v>50.639</v>
       </c>
       <c r="S19" t="n">
-        <v>244.366</v>
+        <v>23.604</v>
       </c>
       <c r="T19" t="n">
-        <v>-49.0036</v>
+        <v>-73.8767</v>
       </c>
       <c r="U19" t="n">
-        <v>18.827</v>
+        <v>17.841</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2056,38 +2056,38 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>019_jpg.rf.52864781a13f7fbec6eb66084ed5823f.jpg</t>
+          <t>019_jpg.rf.57714c5879edaa3f926d048829bcc26c.jpg</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>0.709</v>
+        <v>0.724</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8462</v>
+        <v>0.8545</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8676</v>
+        <v>0.9359</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9658</v>
+        <v>0.9767</v>
       </c>
       <c r="G20" t="n">
-        <v>238.445</v>
+        <v>399.21</v>
       </c>
       <c r="H20" t="n">
-        <v>378.267</v>
+        <v>616.1079999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>262.605</v>
+        <v>437.654</v>
       </c>
       <c r="J20" t="n">
-        <v>78.267</v>
+        <v>103.074</v>
       </c>
       <c r="K20" t="n">
-        <v>300.9711</v>
+        <v>514.4724</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -2095,35 +2095,35 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>258.526</v>
+        <v>381.431</v>
       </c>
       <c r="N20" t="n">
-        <v>81.21599999999999</v>
+        <v>609.873</v>
       </c>
       <c r="O20" t="n">
-        <v>240.07</v>
+        <v>414.441</v>
       </c>
       <c r="P20" t="n">
-        <v>381.706</v>
+        <v>131.638</v>
       </c>
       <c r="Q20" t="n">
-        <v>301.0563</v>
+        <v>479.3733</v>
       </c>
       <c r="R20" t="n">
-        <v>297.73</v>
+        <v>18.84</v>
       </c>
       <c r="S20" t="n">
-        <v>304.274</v>
+        <v>36.807</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0852</v>
+        <v>35.0991</v>
       </c>
       <c r="U20" t="n">
-        <v>0.028</v>
+        <v>7.322</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -2140,38 +2140,38 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>020_jpg.rf.74f065d79dba86d09007843d47da9c23.jpg</t>
+          <t>020_jpg.rf.d729a57510f1353ea9e444ad457c7a68.jpg</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>0.746</v>
+        <v>0.784</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8278</v>
+        <v>0.8299</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9121</v>
+        <v>0.9163</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9409</v>
+        <v>0.9425</v>
       </c>
       <c r="G21" t="n">
-        <v>141.013</v>
+        <v>224.434</v>
       </c>
       <c r="H21" t="n">
-        <v>362.448</v>
+        <v>574.436</v>
       </c>
       <c r="I21" t="n">
-        <v>152.976</v>
+        <v>242.002</v>
       </c>
       <c r="J21" t="n">
-        <v>152.417</v>
+        <v>251.493</v>
       </c>
       <c r="K21" t="n">
-        <v>210.3707</v>
+        <v>323.4209</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2179,35 +2179,35 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>146.415</v>
+        <v>236.07</v>
       </c>
       <c r="N21" t="n">
-        <v>159.861</v>
+        <v>590.05</v>
       </c>
       <c r="O21" t="n">
-        <v>145.97</v>
+        <v>236.07</v>
       </c>
       <c r="P21" t="n">
-        <v>368.953</v>
+        <v>256.682</v>
       </c>
       <c r="Q21" t="n">
-        <v>209.0919</v>
+        <v>333.3683</v>
       </c>
       <c r="R21" t="n">
-        <v>202.658</v>
+        <v>19.473</v>
       </c>
       <c r="S21" t="n">
-        <v>216.649</v>
+        <v>7.881</v>
       </c>
       <c r="T21" t="n">
-        <v>1.2788</v>
+        <v>-9.9474</v>
       </c>
       <c r="U21" t="n">
-        <v>0.612</v>
+        <v>2.984</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -2224,38 +2224,38 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>021_jpg.rf.daa2d35e1c7445885774120f9a2ba2e5.jpg</t>
+          <t>021_jpg.rf.f70910f2157b7937a12cc1541639e31b.jpg</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>0.827</v>
+        <v>0.845</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8323</v>
+        <v>0.831</v>
       </c>
       <c r="E22" t="n">
-        <v>0.914</v>
+        <v>0.9344</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9635</v>
+        <v>0.9629</v>
       </c>
       <c r="G22" t="n">
-        <v>207.944</v>
+        <v>332.785</v>
       </c>
       <c r="H22" t="n">
-        <v>372.706</v>
+        <v>598.045</v>
       </c>
       <c r="I22" t="n">
-        <v>201.202</v>
+        <v>327.121</v>
       </c>
       <c r="J22" t="n">
-        <v>148.708</v>
+        <v>219.952</v>
       </c>
       <c r="K22" t="n">
-        <v>224.0995</v>
+        <v>378.1361</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -2263,35 +2263,35 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>204.778</v>
+        <v>342.529</v>
       </c>
       <c r="N22" t="n">
-        <v>141.667</v>
+        <v>625.648</v>
       </c>
       <c r="O22" t="n">
-        <v>215.889</v>
+        <v>329.52</v>
       </c>
       <c r="P22" t="n">
-        <v>393.333</v>
+        <v>220.513</v>
       </c>
       <c r="Q22" t="n">
-        <v>251.9118</v>
+        <v>405.3438</v>
       </c>
       <c r="R22" t="n">
-        <v>231.061</v>
+        <v>29.272</v>
       </c>
       <c r="S22" t="n">
-        <v>245.066</v>
+        <v>2.464</v>
       </c>
       <c r="T22" t="n">
-        <v>-27.8124</v>
+        <v>-27.2077</v>
       </c>
       <c r="U22" t="n">
-        <v>11.041</v>
+        <v>6.712</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -2308,38 +2308,38 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>022_jpg.rf.54cf361b4e43c6fe903fc4eb1919efb2.jpg</t>
+          <t>022_jpg.rf.af733d3aaa84357f6db47e3607eab176.jpg</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>0.851</v>
+        <v>0.863</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8647</v>
+        <v>0.8631</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.9591</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9792</v>
+        <v>0.9798</v>
       </c>
       <c r="G23" t="n">
-        <v>160.711</v>
+        <v>256.798</v>
       </c>
       <c r="H23" t="n">
-        <v>387.435</v>
+        <v>617.949</v>
       </c>
       <c r="I23" t="n">
-        <v>172.361</v>
+        <v>274.107</v>
       </c>
       <c r="J23" t="n">
-        <v>93.108</v>
+        <v>146.088</v>
       </c>
       <c r="K23" t="n">
-        <v>294.5577</v>
+        <v>472.1783</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2347,35 +2347,35 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>153.111</v>
+        <v>244.667</v>
       </c>
       <c r="N23" t="n">
-        <v>113.333</v>
+        <v>613.552</v>
       </c>
       <c r="O23" t="n">
-        <v>154.778</v>
+        <v>251.565</v>
       </c>
       <c r="P23" t="n">
-        <v>387.222</v>
+        <v>170.626</v>
       </c>
       <c r="Q23" t="n">
-        <v>273.894</v>
+        <v>442.9788</v>
       </c>
       <c r="R23" t="n">
-        <v>274.207</v>
+        <v>12.904</v>
       </c>
       <c r="S23" t="n">
-        <v>294.639</v>
+        <v>33.321</v>
       </c>
       <c r="T23" t="n">
-        <v>20.6638</v>
+        <v>29.1995</v>
       </c>
       <c r="U23" t="n">
-        <v>7.544</v>
+        <v>6.592</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -2392,38 +2392,38 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>023_jpg.rf.66a29ce1f79ebb86d1bed49ace6963fd.jpg</t>
+          <t>023_jpg.rf.56c58a4d6c27e4cb7fd55d2a8f203267.jpg</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>0.862</v>
+        <v>0.849</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.8425</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9436</v>
+        <v>0.9409</v>
       </c>
       <c r="F24" t="n">
-        <v>0.964</v>
+        <v>0.9625</v>
       </c>
       <c r="G24" t="n">
-        <v>177.928</v>
+        <v>278.542</v>
       </c>
       <c r="H24" t="n">
-        <v>369.139</v>
+        <v>589.282</v>
       </c>
       <c r="I24" t="n">
-        <v>190.032</v>
+        <v>303.521</v>
       </c>
       <c r="J24" t="n">
-        <v>131.824</v>
+        <v>207.392</v>
       </c>
       <c r="K24" t="n">
-        <v>237.6242</v>
+        <v>382.7065</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -2431,35 +2431,35 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>191.444</v>
+        <v>290.736</v>
       </c>
       <c r="N24" t="n">
-        <v>149.444</v>
+        <v>603.948</v>
       </c>
       <c r="O24" t="n">
-        <v>180.333</v>
+        <v>310.514</v>
       </c>
       <c r="P24" t="n">
-        <v>381.111</v>
+        <v>238.777</v>
       </c>
       <c r="Q24" t="n">
-        <v>231.933</v>
+        <v>365.7055</v>
       </c>
       <c r="R24" t="n">
-        <v>220.11</v>
+        <v>19.073</v>
       </c>
       <c r="S24" t="n">
-        <v>249.476</v>
+        <v>32.155</v>
       </c>
       <c r="T24" t="n">
-        <v>5.6912</v>
+        <v>17.001</v>
       </c>
       <c r="U24" t="n">
-        <v>2.454</v>
+        <v>4.649</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -2476,38 +2476,38 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>024_jpg.rf.e9ebc38820f6d84a159be64810cf2b42.jpg</t>
+          <t>024_jpg.rf.6ac96b7d688a314bb1618ec97b14c384.jpg</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>0.851</v>
+        <v>0.823</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7379</v>
+        <v>0.7617</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9411</v>
+        <v>0.9348</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.9669</v>
       </c>
       <c r="G25" t="n">
-        <v>273.036</v>
+        <v>434.07</v>
       </c>
       <c r="H25" t="n">
-        <v>354.85</v>
+        <v>572.817</v>
       </c>
       <c r="I25" t="n">
-        <v>266.312</v>
+        <v>420.226</v>
       </c>
       <c r="J25" t="n">
-        <v>109.452</v>
+        <v>166.034</v>
       </c>
       <c r="K25" t="n">
-        <v>245.49</v>
+        <v>407.0188</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2515,35 +2515,35 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>253.667</v>
+        <v>453.375</v>
       </c>
       <c r="N25" t="n">
-        <v>132.778</v>
+        <v>570.937</v>
       </c>
       <c r="O25" t="n">
-        <v>273.111</v>
+        <v>403.438</v>
       </c>
       <c r="P25" t="n">
-        <v>360</v>
+        <v>212.896</v>
       </c>
       <c r="Q25" t="n">
-        <v>228.0527</v>
+        <v>361.5075</v>
       </c>
       <c r="R25" t="n">
-        <v>222.915</v>
+        <v>19.397</v>
       </c>
       <c r="S25" t="n">
-        <v>250.64</v>
+        <v>49.778</v>
       </c>
       <c r="T25" t="n">
-        <v>17.4373</v>
+        <v>45.5113</v>
       </c>
       <c r="U25" t="n">
-        <v>7.646</v>
+        <v>12.589</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -2560,38 +2560,38 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>025_jpg.rf.1d61d795674a24234f5f6c228dda505b.jpg</t>
+          <t>025_jpg.rf.bd162846056d96289581b8b68a4cd15e.jpg</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>0.838</v>
+        <v>0.877</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7889</v>
+        <v>0.7744</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9533</v>
+        <v>0.9493</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.9247</v>
       </c>
       <c r="G26" t="n">
-        <v>110.751</v>
+        <v>176.045</v>
       </c>
       <c r="H26" t="n">
-        <v>96.876</v>
+        <v>154.62</v>
       </c>
       <c r="I26" t="n">
-        <v>162.811</v>
+        <v>263.526</v>
       </c>
       <c r="J26" t="n">
-        <v>327.171</v>
+        <v>520.394</v>
       </c>
       <c r="K26" t="n">
-        <v>236.106</v>
+        <v>376.0893</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2599,35 +2599,35 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>179.222</v>
+        <v>169.832</v>
       </c>
       <c r="N26" t="n">
-        <v>319.444</v>
+        <v>154.492</v>
       </c>
       <c r="O26" t="n">
-        <v>105.333</v>
+        <v>284.095</v>
       </c>
       <c r="P26" t="n">
-        <v>97.22199999999999</v>
+        <v>514.226</v>
       </c>
       <c r="Q26" t="n">
-        <v>234.1843</v>
+        <v>377.4457</v>
       </c>
       <c r="R26" t="n">
-        <v>232.863</v>
+        <v>6.215</v>
       </c>
       <c r="S26" t="n">
-        <v>237.023</v>
+        <v>21.474</v>
       </c>
       <c r="T26" t="n">
-        <v>1.9217</v>
+        <v>-1.3563</v>
       </c>
       <c r="U26" t="n">
-        <v>0.821</v>
+        <v>0.359</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -2644,38 +2644,38 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>026_jpg.rf.d135b38b12794acb3a0dd131078184fe.jpg</t>
+          <t>026_jpg.rf.eb86c226cc0ec30a53e817116a145c45.jpg</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>0.749</v>
+        <v>0.864</v>
       </c>
       <c r="D27" t="n">
-        <v>0.8035</v>
+        <v>0.8015</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9122</v>
+        <v>0.9179</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9613</v>
+        <v>0.9604</v>
       </c>
       <c r="G27" t="n">
-        <v>218.409</v>
+        <v>352.824</v>
       </c>
       <c r="H27" t="n">
-        <v>314.3</v>
+        <v>493.122</v>
       </c>
       <c r="I27" t="n">
-        <v>213.692</v>
+        <v>341.621</v>
       </c>
       <c r="J27" t="n">
-        <v>91.437</v>
+        <v>153.475</v>
       </c>
       <c r="K27" t="n">
-        <v>222.9128</v>
+        <v>339.8322</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2683,35 +2683,35 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>197</v>
+        <v>373.814</v>
       </c>
       <c r="N27" t="n">
-        <v>81.667</v>
+        <v>559.934</v>
       </c>
       <c r="O27" t="n">
-        <v>233.111</v>
+        <v>313.719</v>
       </c>
       <c r="P27" t="n">
-        <v>350.556</v>
+        <v>122.327</v>
       </c>
       <c r="Q27" t="n">
-        <v>271.3029</v>
+        <v>441.7135</v>
       </c>
       <c r="R27" t="n">
-        <v>233.616</v>
+        <v>70.03100000000001</v>
       </c>
       <c r="S27" t="n">
-        <v>259.845</v>
+        <v>41.817</v>
       </c>
       <c r="T27" t="n">
-        <v>-48.3901</v>
+        <v>-101.8814</v>
       </c>
       <c r="U27" t="n">
-        <v>17.836</v>
+        <v>23.065</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -2728,38 +2728,38 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>027_jpg.rf.9be636888e7c341c8c41e6a2766ce5fa.jpg</t>
+          <t>027_jpg.rf.a584ca503394f6f521773f7455447d83.jpg</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>0.741</v>
+        <v>0.783</v>
       </c>
       <c r="D28" t="n">
-        <v>0.8428</v>
+        <v>0.8424</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9305</v>
+        <v>0.9442</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9805</v>
+        <v>0.9741</v>
       </c>
       <c r="G28" t="n">
-        <v>158.226</v>
+        <v>240.644</v>
       </c>
       <c r="H28" t="n">
-        <v>374.373</v>
+        <v>573.205</v>
       </c>
       <c r="I28" t="n">
-        <v>154.988</v>
+        <v>251.272</v>
       </c>
       <c r="J28" t="n">
-        <v>113.059</v>
+        <v>171.246</v>
       </c>
       <c r="K28" t="n">
-        <v>261.3341</v>
+        <v>402.0995</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2767,35 +2767,35 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>145.889</v>
+        <v>243.468</v>
       </c>
       <c r="N28" t="n">
-        <v>120</v>
+        <v>583.634</v>
       </c>
       <c r="O28" t="n">
-        <v>151.444</v>
+        <v>235.004</v>
       </c>
       <c r="P28" t="n">
-        <v>366.667</v>
+        <v>179.038</v>
       </c>
       <c r="Q28" t="n">
-        <v>246.7292</v>
+        <v>404.6842</v>
       </c>
       <c r="R28" t="n">
-        <v>254.672</v>
+        <v>10.805</v>
       </c>
       <c r="S28" t="n">
-        <v>253.633</v>
+        <v>18.038</v>
       </c>
       <c r="T28" t="n">
-        <v>14.6048</v>
+        <v>-2.5847</v>
       </c>
       <c r="U28" t="n">
-        <v>5.919</v>
+        <v>0.639</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -2812,38 +2812,38 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>028_jpg.rf.95ad6712c1dbf3ad22b5803b15393683.jpg</t>
+          <t>028_jpg.rf.9f7173668b1aa0af84f8a71f5d2c5216.jpg</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>0.909</v>
+        <v>0.885</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8242</v>
+        <v>0.8252</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9432</v>
+        <v>0.9425</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9687</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>248.245</v>
+        <v>396.84</v>
       </c>
       <c r="H29" t="n">
-        <v>367.264</v>
+        <v>587.412</v>
       </c>
       <c r="I29" t="n">
-        <v>246.123</v>
+        <v>391.949</v>
       </c>
       <c r="J29" t="n">
-        <v>124.488</v>
+        <v>197.566</v>
       </c>
       <c r="K29" t="n">
-        <v>242.785</v>
+        <v>389.8764</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2851,35 +2851,35 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>247.556</v>
+        <v>395.013</v>
       </c>
       <c r="N29" t="n">
-        <v>125.556</v>
+        <v>631.274</v>
       </c>
       <c r="O29" t="n">
-        <v>247.03</v>
+        <v>404.284</v>
       </c>
       <c r="P29" t="n">
-        <v>394.079</v>
+        <v>198.506</v>
       </c>
       <c r="Q29" t="n">
-        <v>268.524</v>
+        <v>432.8674</v>
       </c>
       <c r="R29" t="n">
-        <v>241.709</v>
+        <v>43.901</v>
       </c>
       <c r="S29" t="n">
-        <v>269.593</v>
+        <v>12.37</v>
       </c>
       <c r="T29" t="n">
-        <v>-25.7391</v>
+        <v>-42.991</v>
       </c>
       <c r="U29" t="n">
-        <v>9.585000000000001</v>
+        <v>9.932</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -2896,38 +2896,38 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>029_jpg.rf.8c2f541015d35e53e936b01eadb34e47.jpg</t>
+          <t>029_jpg.rf.4c2982fbe8c639c7737b0b8f9c9e4168.jpg</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>0.819</v>
+        <v>0.887</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8401999999999999</v>
+        <v>0.8409</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9114</v>
+        <v>0.913</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9517</v>
+        <v>0.9503</v>
       </c>
       <c r="G30" t="n">
-        <v>162.598</v>
+        <v>260.366</v>
       </c>
       <c r="H30" t="n">
-        <v>355.703</v>
+        <v>562.561</v>
       </c>
       <c r="I30" t="n">
-        <v>172.326</v>
+        <v>275.104</v>
       </c>
       <c r="J30" t="n">
-        <v>133.771</v>
+        <v>221.287</v>
       </c>
       <c r="K30" t="n">
-        <v>222.1451</v>
+        <v>341.5921</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2935,35 +2935,35 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>162.689</v>
+        <v>248.531</v>
       </c>
       <c r="N30" t="n">
-        <v>149.254</v>
+        <v>575.099</v>
       </c>
       <c r="O30" t="n">
-        <v>159.925</v>
+        <v>260.027</v>
       </c>
       <c r="P30" t="n">
-        <v>360.42</v>
+        <v>239.052</v>
       </c>
       <c r="Q30" t="n">
-        <v>211.1845</v>
+        <v>336.2437</v>
       </c>
       <c r="R30" t="n">
-        <v>206.449</v>
+        <v>17.241</v>
       </c>
       <c r="S30" t="n">
-        <v>226.988</v>
+        <v>23.3</v>
       </c>
       <c r="T30" t="n">
-        <v>10.9607</v>
+        <v>5.3484</v>
       </c>
       <c r="U30" t="n">
-        <v>5.19</v>
+        <v>1.591</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -2980,38 +2980,38 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>030_jpg.rf.0b36a69f48929ab107a690f010f047a6.jpg</t>
+          <t>030_jpg.rf.9dd5c55183f3b91252cc7a614b646307.jpg</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>0.872</v>
+        <v>0.894</v>
       </c>
       <c r="D31" t="n">
-        <v>0.7991</v>
+        <v>0.8004</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9344</v>
+        <v>0.8598</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9726</v>
+        <v>0.9342</v>
       </c>
       <c r="G31" t="n">
-        <v>210.338</v>
+        <v>338.65</v>
       </c>
       <c r="H31" t="n">
-        <v>348.985</v>
+        <v>549.1130000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>203.506</v>
+        <v>321.279</v>
       </c>
       <c r="J31" t="n">
-        <v>67.274</v>
+        <v>120.459</v>
       </c>
       <c r="K31" t="n">
-        <v>281.7939</v>
+        <v>429.0067</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -3019,35 +3019,35 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>196.444</v>
+        <v>330.647</v>
       </c>
       <c r="N31" t="n">
-        <v>82.77800000000001</v>
+        <v>564.1660000000001</v>
       </c>
       <c r="O31" t="n">
-        <v>205.889</v>
+        <v>316.759</v>
       </c>
       <c r="P31" t="n">
-        <v>349.444</v>
+        <v>130.839</v>
       </c>
       <c r="Q31" t="n">
-        <v>266.8339</v>
+        <v>433.5496</v>
       </c>
       <c r="R31" t="n">
-        <v>266.569</v>
+        <v>17.047</v>
       </c>
       <c r="S31" t="n">
-        <v>282.181</v>
+        <v>11.321</v>
       </c>
       <c r="T31" t="n">
-        <v>14.96</v>
+        <v>-4.5429</v>
       </c>
       <c r="U31" t="n">
-        <v>5.606</v>
+        <v>1.048</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -3064,38 +3064,38 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>031_jpg.rf.f392beb3fe244231d59337504e095a11.jpg</t>
+          <t>031_jpg.rf.7fc14401be79875adabed5e9c77ccde9.jpg</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>0.912</v>
+        <v>0.915</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8142</v>
+        <v>0.8065</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9394</v>
+        <v>0.9475</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9697</v>
+        <v>0.9714</v>
       </c>
       <c r="G32" t="n">
-        <v>243.348</v>
+        <v>390.29</v>
       </c>
       <c r="H32" t="n">
-        <v>374.274</v>
+        <v>595.8339999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>248.409</v>
+        <v>392.655</v>
       </c>
       <c r="J32" t="n">
-        <v>114.099</v>
+        <v>195.423</v>
       </c>
       <c r="K32" t="n">
-        <v>260.2248</v>
+        <v>400.4186</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -3103,35 +3103,35 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>239.778</v>
+        <v>391.293</v>
       </c>
       <c r="N32" t="n">
-        <v>124.444</v>
+        <v>628.717</v>
       </c>
       <c r="O32" t="n">
-        <v>252.556</v>
+        <v>382.894</v>
       </c>
       <c r="P32" t="n">
-        <v>395.556</v>
+        <v>200.97</v>
       </c>
       <c r="Q32" t="n">
-        <v>271.412</v>
+        <v>427.8294</v>
       </c>
       <c r="R32" t="n">
-        <v>249.855</v>
+        <v>32.898</v>
       </c>
       <c r="S32" t="n">
-        <v>281.488</v>
+        <v>11.227</v>
       </c>
       <c r="T32" t="n">
-        <v>-11.1872</v>
+        <v>-27.4107</v>
       </c>
       <c r="U32" t="n">
-        <v>4.122</v>
+        <v>6.407</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -3148,38 +3148,38 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>032_jpg.rf.a1483732b3cfe35413834e422f2e1c8f.jpg</t>
+          <t>032_jpg.rf.1557b97911ef21a82002883aed8fdabe.jpg</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>0.83</v>
+        <v>0.902</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8572</v>
+        <v>0.85</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9434</v>
+        <v>0.9406</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9739</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>138.14</v>
+        <v>218.228</v>
       </c>
       <c r="H33" t="n">
-        <v>370.971</v>
+        <v>586.021</v>
       </c>
       <c r="I33" t="n">
-        <v>153.551</v>
+        <v>242.284</v>
       </c>
       <c r="J33" t="n">
-        <v>116.747</v>
+        <v>198.739</v>
       </c>
       <c r="K33" t="n">
-        <v>254.69</v>
+        <v>388.0278</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -3187,35 +3187,35 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>146.444</v>
+        <v>215.025</v>
       </c>
       <c r="N33" t="n">
-        <v>136.667</v>
+        <v>627.573</v>
       </c>
       <c r="O33" t="n">
-        <v>138.111</v>
+        <v>235.761</v>
       </c>
       <c r="P33" t="n">
-        <v>392.778</v>
+        <v>201.957</v>
       </c>
       <c r="Q33" t="n">
-        <v>256.2467</v>
+        <v>426.1203</v>
       </c>
       <c r="R33" t="n">
-        <v>234.451</v>
+        <v>41.675</v>
       </c>
       <c r="S33" t="n">
-        <v>276.462</v>
+        <v>7.273</v>
       </c>
       <c r="T33" t="n">
-        <v>-1.5567</v>
+        <v>-38.0925</v>
       </c>
       <c r="U33" t="n">
-        <v>0.608</v>
+        <v>8.939</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -3232,38 +3232,38 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>033_jpg.rf.4e99d92e4c1804a1a445d3da4dd329bc.jpg</t>
+          <t>033_jpg.rf.d3280fd4c1a5d0ad4febcd03cbb7b159.jpg</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>0.802</v>
+        <v>0.871</v>
       </c>
       <c r="D34" t="n">
-        <v>0.7511</v>
+        <v>0.8063</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9147</v>
+        <v>0.9358</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9702</v>
+        <v>0.9757</v>
       </c>
       <c r="G34" t="n">
-        <v>197.891</v>
+        <v>325.741</v>
       </c>
       <c r="H34" t="n">
-        <v>345.336</v>
+        <v>558.623</v>
       </c>
       <c r="I34" t="n">
-        <v>189.968</v>
+        <v>306.661</v>
       </c>
       <c r="J34" t="n">
-        <v>92.273</v>
+        <v>144.948</v>
       </c>
       <c r="K34" t="n">
-        <v>253.1865</v>
+        <v>414.1144</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -3271,35 +3271,35 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>172.556</v>
+        <v>339.445</v>
       </c>
       <c r="N34" t="n">
-        <v>101.111</v>
+        <v>588.073</v>
       </c>
       <c r="O34" t="n">
-        <v>213.111</v>
+        <v>276.574</v>
       </c>
       <c r="P34" t="n">
-        <v>371.111</v>
+        <v>162.031</v>
       </c>
       <c r="Q34" t="n">
-        <v>273.0289</v>
+        <v>430.6561</v>
       </c>
       <c r="R34" t="n">
-        <v>245.535</v>
+        <v>32.482</v>
       </c>
       <c r="S34" t="n">
-        <v>279.797</v>
+        <v>34.598</v>
       </c>
       <c r="T34" t="n">
-        <v>-19.8424</v>
+        <v>-16.5416</v>
       </c>
       <c r="U34" t="n">
-        <v>7.267</v>
+        <v>3.841</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>⚠️是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>234.86</v>
+        <v>20.852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>259.513</v>
+        <v>23.3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>304.274</v>
+        <v>70.03100000000001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.2226</v>
+        <v>31.6287</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-5.2141</v>
+        <v>-12.6336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.658</v>
+        <v>7.473</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52.2689</v>
+        <v>101.8814</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.774</v>
+        <v>0.843</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
